--- a/data-dictionary/palmer_penguins_metadata.xlsx
+++ b/data-dictionary/palmer_penguins_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phill\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phil_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64305037-69B6-40DB-8937-2FE3C651C804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B61B3BF-FB6E-4202-B224-6853813CD6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4E5D4E54-1469-4C7B-BD01-AB2E136BF4DE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4E5D4E54-1469-4C7B-BD01-AB2E136BF4DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
-  <si>
-    <t>Variable name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
   <si>
     <t>Type</t>
   </si>
@@ -51,9 +48,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Notes / Valid Range</t>
-  </si>
-  <si>
     <t>studyName</t>
   </si>
   <si>
@@ -596,13 +590,25 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Notes_Valid Range</t>
+  </si>
+  <si>
+    <t>Missing values</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,319 +1007,373 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{223DAE6A-5DAF-4E5C-A7D8-3FC50E0D922E}">
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" customWidth="1"/>
-    <col min="2" max="2" width="17.08984375" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="30">
       <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="90">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="105">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="134.25">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="127.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="45">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="90">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60">
+      <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="45">
+      <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="B10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45">
+      <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45">
+      <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="45">
+      <c r="A13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="45">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="60">
+      <c r="A15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="75">
+      <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="87" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="75">
+      <c r="A17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="E17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="60">
+      <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>61</v>
+      <c r="F18" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1324,98 +1384,98 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086154FD-42A9-4B49-81DB-403F29B75025}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30">
+      <c r="A2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="30">
+      <c r="A3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="1:2" ht="30">
+      <c r="A6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="B6" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="30">
       <c r="A7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30">
+      <c r="A8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:2" ht="45">
+      <c r="A9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:2" ht="135">
+      <c r="A10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="1:2" ht="30">
+      <c r="A11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
